--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8258,0.0514,0.0182,0.0237</t>
-  </si>
-  <si>
-    <t>0.8056,0.0112,0.0051,0.1271</t>
-  </si>
-  <si>
-    <t>0.6677,0.0427,0.0355,0.1710</t>
-  </si>
-  <si>
-    <t>0.8305,0.0325,0.0057,0.0315</t>
-  </si>
-  <si>
-    <t>0.7282,0.1083,0.0131,0.0284</t>
-  </si>
-  <si>
-    <t>0.8040,0.0531,0.0061,0.0222</t>
-  </si>
-  <si>
-    <t>0.8234,0.0371,0.0059,0.0304</t>
-  </si>
-  <si>
-    <t>0.5966,0.0911,0.0138,0.1009</t>
-  </si>
-  <si>
-    <t>0.8306,0.0270,0.0030,0.0292</t>
-  </si>
-  <si>
-    <t>0.7154,0.0948,0.0099,0.0374</t>
-  </si>
-  <si>
-    <t>0.7215,0.0780,0.0213,0.0598</t>
-  </si>
-  <si>
-    <t>0.7226,0.0864,0.0089,0.0263</t>
-  </si>
-  <si>
-    <t>0.7091,0.0533,0.0512,0.0820</t>
-  </si>
-  <si>
-    <t>0.8092,0.0592,0.1403,0.0109</t>
-  </si>
-  <si>
-    <t>0.8953,0.0096,0.0696,0.0169</t>
-  </si>
-  <si>
-    <t>0.6788,0.1226,0.0789,0.0493</t>
-  </si>
-  <si>
-    <t>0.7083,0.1183,0.0371,0.0385</t>
-  </si>
-  <si>
-    <t>0.0936,0.8782,0.0653,0.0077</t>
-  </si>
-  <si>
-    <t>0.0141,0.9774,0.0135,0.0038</t>
-  </si>
-  <si>
-    <t>0.8593,0.0703,0.0067,0.0109</t>
-  </si>
-  <si>
-    <t>0.2414,0.6880,0.0940,0.0186</t>
-  </si>
-  <si>
-    <t>0.0051,0.9852,0.0763,0.0070</t>
-  </si>
-  <si>
-    <t>0.9501,0.0071,0.0084,0.0055</t>
-  </si>
-  <si>
-    <t>0.9254,0.0037,0.0103,0.0429</t>
-  </si>
-  <si>
-    <t>0.8216,0.0232,0.1621,0.0072</t>
-  </si>
-  <si>
-    <t>0.4973,0.0622,0.4871,0.0273</t>
-  </si>
-  <si>
-    <t>0.3338,0.0363,0.7557,0.0074</t>
-  </si>
-  <si>
-    <t>0.6745,0.0241,0.4587,0.0029</t>
-  </si>
-  <si>
-    <t>0.5303,0.0182,0.6136,0.0072</t>
-  </si>
-  <si>
-    <t>0.6328,0.1221,0.0246,0.0544</t>
-  </si>
-  <si>
-    <t>0.7045,0.0247,0.0147,0.1937</t>
-  </si>
-  <si>
-    <t>0.0087,0.6824,0.9587,0.0016</t>
-  </si>
-  <si>
-    <t>0.3209,0.5874,0.0852,0.0173</t>
-  </si>
-  <si>
-    <t>0.6144,0.1891,0.0254,0.0336</t>
-  </si>
-  <si>
-    <t>0.6308,0.0905,0.0398,0.1357</t>
-  </si>
-  <si>
-    <t>0.6382,0.0965,0.0073,0.0443</t>
-  </si>
-  <si>
-    <t>0.6121,0.2601,0.0278,0.0146</t>
-  </si>
-  <si>
-    <t>0.2342,0.4587,0.4114,0.0520</t>
-  </si>
-  <si>
-    <t>0.6455,0.0083,0.4209,0.0079</t>
-  </si>
-  <si>
-    <t>0.7359,0.0103,0.3763,0.0046</t>
-  </si>
-  <si>
-    <t>0.8514,0.0323,0.0626,0.0275</t>
-  </si>
-  <si>
-    <t>0.3835,0.3427,0.3510,0.0370</t>
-  </si>
-  <si>
-    <t>0.3181,0.5948,0.0852,0.0237</t>
-  </si>
-  <si>
-    <t>0.6731,0.0389,0.3113,0.0174</t>
-  </si>
-  <si>
-    <t>0.6610,0.1274,0.0108,0.0329</t>
-  </si>
-  <si>
-    <t>0.7597,0.1684,0.0091,0.0098</t>
-  </si>
-  <si>
-    <t>0.1437,0.8365,0.1031,0.0097</t>
-  </si>
-  <si>
-    <t>0.8712,0.0937,0.0063,0.0072</t>
-  </si>
-  <si>
-    <t>0.2779,0.1643,0.6552,0.0221</t>
-  </si>
-  <si>
-    <t>0.1195,0.0535,0.8933,0.0020</t>
-  </si>
-  <si>
-    <t>0.5548,0.0163,0.5286,0.0111</t>
-  </si>
-  <si>
-    <t>0.7519,0.0089,0.2856,0.0138</t>
-  </si>
-  <si>
-    <t>0.0489,0.0762,0.9661,0.0003</t>
-  </si>
-  <si>
-    <t>0.5323,0.2557,0.2816,0.0066</t>
-  </si>
-  <si>
-    <t>0.8291,0.0249,0.0032,0.0405</t>
-  </si>
-  <si>
-    <t>0.6756,0.0891,0.0268,0.0877</t>
-  </si>
-  <si>
-    <t>0.6580,0.1896,0.0226,0.0204</t>
-  </si>
-  <si>
-    <t>0.3422,0.4467,0.3289,0.0388</t>
-  </si>
-  <si>
-    <t>0.8257,0.0365,0.0072,0.0381</t>
-  </si>
-  <si>
-    <t>0.8685,0.0280,0.0056,0.0258</t>
-  </si>
-  <si>
-    <t>0.6942,0.1850,0.0130,0.0120</t>
-  </si>
-  <si>
-    <t>0.0021,0.9059,0.9732,0.0007</t>
-  </si>
-  <si>
-    <t>0.4149,0.1075,0.5717,0.0212</t>
-  </si>
-  <si>
-    <t>0.2253,0.1059,0.8006,0.0062</t>
-  </si>
-  <si>
-    <t>0.0011,0.9817,0.9133,0.0011</t>
-  </si>
-  <si>
-    <t>0.0932,0.0324,0.9405,0.0011</t>
-  </si>
-  <si>
-    <t>0.4282,0.5864,0.0138,0.0052</t>
-  </si>
-  <si>
-    <t>0.0028,0.9970,0.0101,0.0002</t>
-  </si>
-  <si>
-    <t>0.8160,0.0466,0.0405,0.0353</t>
-  </si>
-  <si>
-    <t>0.8274,0.0257,0.0126,0.0601</t>
-  </si>
-  <si>
-    <t>0.3351,0.6048,0.1911,0.0272</t>
-  </si>
-  <si>
-    <t>0.2847,0.1859,0.7009,0.0047</t>
-  </si>
-  <si>
-    <t>0.0729,0.4365,0.8210,0.0142</t>
-  </si>
-  <si>
-    <t>0.0029,0.9787,0.8011,0.0006</t>
-  </si>
-  <si>
-    <t>0.0063,0.9093,0.9231,0.0018</t>
-  </si>
-  <si>
-    <t>0.7898,0.0546,0.0250,0.0465</t>
-  </si>
-  <si>
-    <t>0.6394,0.0701,0.0121,0.1156</t>
-  </si>
-  <si>
-    <t>0.8935,0.0056,0.0016,0.0562</t>
-  </si>
-  <si>
-    <t>0.6817,0.0416,0.0279,0.1847</t>
-  </si>
-  <si>
-    <t>0.7974,0.0104,0.0088,0.1724</t>
-  </si>
-  <si>
-    <t>0.7705,0.0152,0.0175,0.1997</t>
-  </si>
-  <si>
-    <t>0.0617,0.7620,0.7047,0.0124</t>
-  </si>
-  <si>
-    <t>0.3748,0.2377,0.4822,0.0291</t>
-  </si>
-  <si>
-    <t>0.7765,0.0517,0.1060,0.0273</t>
-  </si>
-  <si>
-    <t>0.0380,0.1955,0.9505,0.0023</t>
-  </si>
-  <si>
-    <t>0.0293,0.8448,0.7321,0.0028</t>
-  </si>
-  <si>
-    <t>0.0879,0.8394,0.4040,0.0049</t>
-  </si>
-  <si>
-    <t>0.4513,0.3630,0.0313,0.0252</t>
-  </si>
-  <si>
-    <t>0.7316,0.0867,0.0117,0.0381</t>
-  </si>
-  <si>
-    <t>0.6776,0.2297,0.0284,0.0138</t>
-  </si>
-  <si>
-    <t>0.8172,0.0655,0.0105,0.0242</t>
-  </si>
-  <si>
-    <t>0.8110,0.0288,0.0018,0.0243</t>
-  </si>
-  <si>
-    <t>0.8193,0.0377,0.0061,0.0322</t>
-  </si>
-  <si>
-    <t>0.8910,0.0291,0.0047,0.0131</t>
-  </si>
-  <si>
-    <t>0.8809,0.0309,0.0065,0.0201</t>
-  </si>
-  <si>
-    <t>0.7764,0.1305,0.0223,0.0156</t>
-  </si>
-  <si>
-    <t>0.7936,0.0845,0.0074,0.0160</t>
-  </si>
-  <si>
-    <t>0.8032,0.1008,0.0170,0.0172</t>
-  </si>
-  <si>
-    <t>0.8304,0.0749,0.0087,0.0141</t>
-  </si>
-  <si>
-    <t>0.8420,0.0402,0.0055,0.0189</t>
-  </si>
-  <si>
-    <t>0.7192,0.0568,0.0174,0.0814</t>
-  </si>
-  <si>
-    <t>0.8490,0.0322,0.0079,0.0312</t>
-  </si>
-  <si>
-    <t>0.8642,0.0364,0.0184,0.0321</t>
-  </si>
-  <si>
-    <t>0.1773,0.0301,0.8883,0.0048</t>
-  </si>
-  <si>
-    <t>0.4330,0.2409,0.4087,0.0411</t>
-  </si>
-  <si>
-    <t>0.8852,0.0240,0.0479,0.0205</t>
-  </si>
-  <si>
-    <t>0.8644,0.0034,0.1963,0.0029</t>
-  </si>
-  <si>
-    <t>0.1466,0.7835,0.0991,0.0122</t>
-  </si>
-  <si>
-    <t>0.0872,0.8748,0.0873,0.0152</t>
-  </si>
-  <si>
-    <t>0.1806,0.6853,0.0600,0.0413</t>
-  </si>
-  <si>
-    <t>0.6044,0.2276,0.0276,0.0222</t>
-  </si>
-  <si>
-    <t>0.4506,0.3173,0.0401,0.0376</t>
-  </si>
-  <si>
-    <t>0.3652,0.5400,0.0197,0.0138</t>
-  </si>
-  <si>
-    <t>0.6335,0.2878,0.0217,0.0096</t>
-  </si>
-  <si>
-    <t>0.6474,0.1329,0.0192,0.0398</t>
-  </si>
-  <si>
-    <t>0.8675,0.0232,0.0734,0.0179</t>
-  </si>
-  <si>
-    <t>0.7363,0.0884,0.1028,0.0598</t>
-  </si>
-  <si>
-    <t>0.8604,0.0310,0.0283,0.0345</t>
-  </si>
-  <si>
-    <t>0.4841,0.2367,0.0636,0.0764</t>
-  </si>
-  <si>
-    <t>0.5502,0.4429,0.0097,0.0049</t>
-  </si>
-  <si>
-    <t>0.5761,0.3477,0.0134,0.0079</t>
-  </si>
-  <si>
-    <t>0.2703,0.6138,0.1466,0.0155</t>
-  </si>
-  <si>
-    <t>0.1805,0.8296,0.0067,0.0054</t>
-  </si>
-  <si>
-    <t>0.7019,0.2404,0.0098,0.0079</t>
-  </si>
-  <si>
-    <t>0.4787,0.3629,0.0374,0.0198</t>
-  </si>
-  <si>
-    <t>0.7175,0.1037,0.0101,0.0326</t>
-  </si>
-  <si>
-    <t>0.8547,0.0298,0.0052,0.0229</t>
-  </si>
-  <si>
-    <t>0.8103,0.0170,0.0036,0.0722</t>
-  </si>
-  <si>
-    <t>0.7067,0.1334,0.0341,0.0349</t>
-  </si>
-  <si>
-    <t>0.6053,0.0871,0.0246,0.1146</t>
-  </si>
-  <si>
-    <t>0.7905,0.0315,0.0076,0.0609</t>
-  </si>
-  <si>
-    <t>0.7829,0.0568,0.0151,0.0423</t>
-  </si>
-  <si>
-    <t>0.6127,0.0738,0.0221,0.1333</t>
-  </si>
-  <si>
-    <t>0.7397,0.1218,0.0190,0.0262</t>
-  </si>
-  <si>
-    <t>0.1754,0.3634,0.6585,0.0209</t>
-  </si>
-  <si>
-    <t>0.6282,0.0668,0.2822,0.0110</t>
-  </si>
-  <si>
-    <t>0.1373,0.2360,0.8406,0.0022</t>
-  </si>
-  <si>
-    <t>0.6206,0.0511,0.3700,0.0094</t>
-  </si>
-  <si>
-    <t>0.8709,0.0260,0.0343,0.0218</t>
-  </si>
-  <si>
-    <t>0.8083,0.0382,0.0217,0.0535</t>
-  </si>
-  <si>
-    <t>0.7742,0.0418,0.1404,0.0468</t>
-  </si>
-  <si>
-    <t>0.8914,0.0301,0.0063,0.0165</t>
-  </si>
-  <si>
-    <t>0.6728,0.0551,0.0185,0.1423</t>
-  </si>
-  <si>
-    <t>0.7202,0.0383,0.0205,0.1811</t>
-  </si>
-  <si>
-    <t>0.8163,0.0408,0.0171,0.0655</t>
-  </si>
-  <si>
-    <t>0.5705,0.0457,0.0209,0.2505</t>
-  </si>
-  <si>
-    <t>0.1058,0.6443,0.6143,0.0401</t>
-  </si>
-  <si>
-    <t>0.7365,0.0839,0.0084,0.0239</t>
-  </si>
-  <si>
-    <t>0.5269,0.2976,0.0510,0.0427</t>
-  </si>
-  <si>
-    <t>0.7598,0.1114,0.0111,0.0176</t>
-  </si>
-  <si>
-    <t>0.5742,0.1976,0.0197,0.0368</t>
-  </si>
-  <si>
-    <t>0.8661,0.0248,0.0151,0.0498</t>
-  </si>
-  <si>
-    <t>0.8995,0.0165,0.0051,0.0296</t>
-  </si>
-  <si>
-    <t>0.7688,0.0734,0.0098,0.0301</t>
-  </si>
-  <si>
-    <t>0.0019,0.9430,0.9484,0.0026</t>
-  </si>
-  <si>
-    <t>0.9286,0.0147,0.0030,0.0118</t>
-  </si>
-  <si>
-    <t>0.8365,0.0245,0.0081,0.0505</t>
-  </si>
-  <si>
-    <t>0.6790,0.1545,0.0196,0.0308</t>
-  </si>
-  <si>
-    <t>0.7526,0.0479,0.0129,0.0675</t>
-  </si>
-  <si>
-    <t>0.7397,0.1619,0.0235,0.0198</t>
-  </si>
-  <si>
-    <t>0.6842,0.0988,0.0189,0.0539</t>
-  </si>
-  <si>
-    <t>0.9333,0.0209,0.0015,0.0053</t>
-  </si>
-  <si>
-    <t>0.7753,0.1344,0.0218,0.0139</t>
-  </si>
-  <si>
-    <t>0.7437,0.0811,0.0030,0.0103</t>
-  </si>
-  <si>
-    <t>0.7316,0.0591,0.0131,0.0531</t>
-  </si>
-  <si>
-    <t>0.7062,0.1299,0.0145,0.0217</t>
-  </si>
-  <si>
-    <t>0.7832,0.0600,0.0215,0.0477</t>
-  </si>
-  <si>
-    <t>0.8521,0.0763,0.0038,0.0063</t>
-  </si>
-  <si>
-    <t>0.8554,0.0314,0.0085,0.0411</t>
-  </si>
-  <si>
-    <t>0.7497,0.0742,0.0248,0.0632</t>
-  </si>
-  <si>
-    <t>0.6176,0.1825,0.0227,0.0307</t>
-  </si>
-  <si>
-    <t>0.2745,0.5143,0.0156,0.0256</t>
-  </si>
-  <si>
-    <t>0.7216,0.1717,0.0138,0.0133</t>
-  </si>
-  <si>
-    <t>0.7034,0.3211,0.0081,0.0035</t>
-  </si>
-  <si>
-    <t>0.8013,0.0294,0.0083,0.0754</t>
-  </si>
-  <si>
-    <t>0.6866,0.1538,0.0144,0.0178</t>
-  </si>
-  <si>
-    <t>0.8941,0.0376,0.0064,0.0114</t>
-  </si>
-  <si>
-    <t>0.5511,0.3738,0.0189,0.0111</t>
-  </si>
-  <si>
-    <t>0.7463,0.0677,0.0249,0.0650</t>
-  </si>
-  <si>
-    <t>0.0010,0.7284,0.9940,0.0001</t>
-  </si>
-  <si>
-    <t>0.4482,0.3652,0.0076,0.0143</t>
-  </si>
-  <si>
-    <t>0.2596,0.0391,0.8361,0.0015</t>
-  </si>
-  <si>
-    <t>0.4485,0.0463,0.5730,0.0189</t>
-  </si>
-  <si>
-    <t>0.8998,0.0267,0.0337,0.0153</t>
-  </si>
-  <si>
-    <t>0.0855,0.7486,0.5955,0.0241</t>
-  </si>
-  <si>
-    <t>0.2268,0.1648,0.7323,0.0132</t>
-  </si>
-  <si>
-    <t>0.0684,0.0981,0.8982,0.0014</t>
-  </si>
-  <si>
-    <t>0.1192,0.0389,0.9059,0.0018</t>
-  </si>
-  <si>
-    <t>0.8403,0.0261,0.0215,0.0449</t>
-  </si>
-  <si>
-    <t>0.8396,0.0362,0.0823,0.0257</t>
-  </si>
-  <si>
-    <t>0.7000,0.0631,0.1176,0.0957</t>
-  </si>
-  <si>
-    <t>0.6191,0.1543,0.0770,0.0855</t>
-  </si>
-  <si>
-    <t>0.6947,0.1005,0.0908,0.0726</t>
-  </si>
-  <si>
-    <t>0.5314,0.3382,0.1152,0.0313</t>
-  </si>
-  <si>
-    <t>0.8960,0.0108,0.0056,0.0446</t>
-  </si>
-  <si>
-    <t>0.6987,0.0719,0.0688,0.0958</t>
-  </si>
-  <si>
-    <t>0.2302,0.6472,0.0159,0.0145</t>
-  </si>
-  <si>
-    <t>0.6842,0.2486,0.0070,0.0058</t>
-  </si>
-  <si>
-    <t>0.8723,0.0849,0.0028,0.0038</t>
-  </si>
-  <si>
-    <t>0.7482,0.0927,0.0130,0.0249</t>
-  </si>
-  <si>
-    <t>0.5091,0.2700,0.0207,0.0319</t>
-  </si>
-  <si>
-    <t>0.8790,0.0224,0.0076,0.0328</t>
-  </si>
-  <si>
-    <t>0.9211,0.0384,0.0058,0.0046</t>
-  </si>
-  <si>
-    <t>0.9624,0.0030,0.0063,0.0105</t>
-  </si>
-  <si>
-    <t>0.8679,0.0589,0.0327,0.0127</t>
-  </si>
-  <si>
-    <t>0.7850,0.0810,0.0752,0.0390</t>
-  </si>
-  <si>
-    <t>0.4616,0.0910,0.5778,0.0124</t>
-  </si>
-  <si>
-    <t>0.7498,0.0355,0.2096,0.0195</t>
-  </si>
-  <si>
-    <t>0.6161,0.0913,0.2179,0.0676</t>
-  </si>
-  <si>
-    <t>0.4481,0.0937,0.5282,0.0284</t>
-  </si>
-  <si>
-    <t>0.4934,0.1328,0.4022,0.0177</t>
-  </si>
-  <si>
-    <t>0.7623,0.1245,0.0097,0.0135</t>
-  </si>
-  <si>
-    <t>0.8172,0.0633,0.0082,0.0223</t>
-  </si>
-  <si>
-    <t>0.6296,0.0992,0.0289,0.0913</t>
-  </si>
-  <si>
-    <t>0.8233,0.0602,0.0090,0.0209</t>
-  </si>
-  <si>
-    <t>0.8162,0.0470,0.0062,0.0242</t>
-  </si>
-  <si>
-    <t>0.7607,0.0674,0.0106,0.0377</t>
-  </si>
-  <si>
-    <t>0.7159,0.1375,0.0155,0.0156</t>
-  </si>
-  <si>
-    <t>0.5335,0.3163,0.0272,0.0163</t>
-  </si>
-  <si>
-    <t>0.4985,0.0754,0.2444,0.1570</t>
-  </si>
-  <si>
-    <t>0.8211,0.0472,0.0164,0.0348</t>
-  </si>
-  <si>
-    <t>0.8035,0.0518,0.0391,0.0470</t>
-  </si>
-  <si>
-    <t>0.3342,0.0494,0.6905,0.0135</t>
-  </si>
-  <si>
-    <t>0.0479,0.2051,0.9290,0.0073</t>
-  </si>
-  <si>
-    <t>0.7403,0.0697,0.1805,0.0166</t>
-  </si>
-  <si>
-    <t>0.1283,0.1603,0.8861,0.0023</t>
-  </si>
-  <si>
-    <t>0.5749,0.0674,0.4129,0.0115</t>
-  </si>
-  <si>
-    <t>0.1626,0.1660,0.8297,0.0046</t>
-  </si>
-  <si>
-    <t>0.5806,0.0091,0.4550,0.0164</t>
-  </si>
-  <si>
-    <t>0.2527,0.0479,0.7310,0.0204</t>
-  </si>
-  <si>
-    <t>0.9555,0.0070,0.0212,0.0046</t>
-  </si>
-  <si>
-    <t>0.8873,0.0088,0.0375,0.0382</t>
-  </si>
-  <si>
-    <t>0.8839,0.0183,0.0081,0.0345</t>
-  </si>
-  <si>
-    <t>0.6988,0.0755,0.0077,0.0342</t>
-  </si>
-  <si>
-    <t>0.7106,0.0241,0.0045,0.1037</t>
-  </si>
-  <si>
-    <t>0.8380,0.0499,0.0030,0.0144</t>
-  </si>
-  <si>
-    <t>0.7186,0.1151,0.0241,0.0370</t>
-  </si>
-  <si>
-    <t>0.7817,0.0448,0.0118,0.0568</t>
-  </si>
-  <si>
-    <t>0.7438,0.0629,0.0068,0.0464</t>
-  </si>
-  <si>
-    <t>0.8205,0.0349,0.0063,0.0429</t>
-  </si>
-  <si>
-    <t>0.8158,0.0737,0.0097,0.0181</t>
-  </si>
-  <si>
-    <t>0.2979,0.1237,0.6554,0.0187</t>
-  </si>
-  <si>
-    <t>0.1593,0.1116,0.8403,0.0073</t>
-  </si>
-  <si>
-    <t>0.1882,0.2914,0.7065,0.0214</t>
-  </si>
-  <si>
-    <t>0.8956,0.0114,0.0800,0.0109</t>
-  </si>
-  <si>
-    <t>0.5724,0.0256,0.4865,0.0067</t>
-  </si>
-  <si>
-    <t>0.8848,0.0255,0.0044,0.0165</t>
-  </si>
-  <si>
-    <t>0.3994,0.0573,0.5960,0.0161</t>
-  </si>
-  <si>
-    <t>0.7550,0.0514,0.0564,0.0888</t>
-  </si>
-  <si>
-    <t>0.8529,0.0284,0.0183,0.0548</t>
-  </si>
-  <si>
-    <t>0.8169,0.0115,0.0099,0.1425</t>
-  </si>
-  <si>
-    <t>0.9341,0.0052,0.0034,0.0313</t>
-  </si>
-  <si>
-    <t>0.7766,0.0156,0.0121,0.1585</t>
-  </si>
-  <si>
-    <t>0.7487,0.0036,0.0018,0.2631</t>
-  </si>
-  <si>
-    <t>0.8387,0.0246,0.0105,0.0416</t>
+    <t>0.9490,0.0114,0.0187,0.0089</t>
+  </si>
+  <si>
+    <t>0.0124,0.0005,0.0018,0.9937</t>
+  </si>
+  <si>
+    <t>0.9051,0.0027,0.0009,0.1156</t>
+  </si>
+  <si>
+    <t>0.1289,0.0075,0.0034,0.9318</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9956,0.0004,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9830,0.0024,0.0018,0.0098</t>
+  </si>
+  <si>
+    <t>0.9958,0.0004,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9893,0.0040,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9914,0.0025,0.0018,0.0015</t>
+  </si>
+  <si>
+    <t>0.9862,0.0083,0.0029,0.0009</t>
+  </si>
+  <si>
+    <t>0.9969,0.0002,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.8711,0.0278,0.0837,0.0014</t>
+  </si>
+  <si>
+    <t>0.1050,0.0448,0.8697,0.0040</t>
+  </si>
+  <si>
+    <t>0.3637,0.0024,0.8485,0.0001</t>
+  </si>
+  <si>
+    <t>0.0736,0.0023,0.9612,0.0009</t>
+  </si>
+  <si>
+    <t>0.7915,0.0051,0.2936,0.0053</t>
+  </si>
+  <si>
+    <t>0.0004,0.9980,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.0219,0.9686,0.0026,0.0026</t>
+  </si>
+  <si>
+    <t>0.0088,0.9758,0.0102,0.0075</t>
+  </si>
+  <si>
+    <t>0.0005,0.9977,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.7672,0.0042,0.2861,0.0097</t>
+  </si>
+  <si>
+    <t>0.0336,0.0061,0.9474,0.0083</t>
+  </si>
+  <si>
+    <t>0.0139,0.0009,0.9918,0.0004</t>
+  </si>
+  <si>
+    <t>0.0078,0.0032,0.9827,0.0041</t>
+  </si>
+  <si>
+    <t>0.0031,0.0024,0.9889,0.0053</t>
+  </si>
+  <si>
+    <t>0.4230,0.0115,0.7331,0.0048</t>
+  </si>
+  <si>
+    <t>0.0040,0.0015,0.9774,0.0303</t>
+  </si>
+  <si>
+    <t>0.2394,0.8174,0.0086,0.0005</t>
+  </si>
+  <si>
+    <t>0.2130,0.2578,0.6062,0.0047</t>
+  </si>
+  <si>
+    <t>0.0030,0.0238,0.9898,0.0071</t>
+  </si>
+  <si>
+    <t>0.0038,0.9570,0.1065,0.0002</t>
+  </si>
+  <si>
+    <t>0.8870,0.0456,0.0483,0.0224</t>
+  </si>
+  <si>
+    <t>0.1140,0.0123,0.8658,0.0377</t>
+  </si>
+  <si>
+    <t>0.6753,0.3269,0.0434,0.0040</t>
+  </si>
+  <si>
+    <t>0.0076,0.9833,0.1823,0.0014</t>
+  </si>
+  <si>
+    <t>0.0091,0.7240,0.8795,0.0022</t>
+  </si>
+  <si>
+    <t>0.0320,0.0065,0.8410,0.1324</t>
+  </si>
+  <si>
+    <t>0.0558,0.0600,0.9508,0.0030</t>
+  </si>
+  <si>
+    <t>0.1278,0.0177,0.9143,0.0034</t>
+  </si>
+  <si>
+    <t>0.0155,0.0123,0.9760,0.0045</t>
+  </si>
+  <si>
+    <t>0.0098,0.9742,0.0107,0.0024</t>
+  </si>
+  <si>
+    <t>0.0181,0.0038,0.9783,0.0041</t>
+  </si>
+  <si>
+    <t>0.0747,0.3039,0.0018,0.5099</t>
+  </si>
+  <si>
+    <t>0.0057,0.9820,0.0031,0.0099</t>
+  </si>
+  <si>
+    <t>0.0020,0.9876,0.0109,0.0078</t>
+  </si>
+  <si>
+    <t>0.0001,0.9986,0.0067,0.0034</t>
+  </si>
+  <si>
+    <t>0.0013,0.0188,0.9926,0.0030</t>
+  </si>
+  <si>
+    <t>0.0110,0.0777,0.9779,0.0010</t>
+  </si>
+  <si>
+    <t>0.0352,0.0083,0.9684,0.0016</t>
+  </si>
+  <si>
+    <t>0.0136,0.0013,0.9908,0.0006</t>
+  </si>
+  <si>
+    <t>0.0015,0.0032,0.9926,0.0075</t>
+  </si>
+  <si>
+    <t>0.0011,0.3899,0.9898,0.0005</t>
+  </si>
+  <si>
+    <t>0.9457,0.0974,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9713,0.0038,0.0257,0.0013</t>
+  </si>
+  <si>
+    <t>0.9850,0.0019,0.0013,0.0085</t>
+  </si>
+  <si>
+    <t>0.0022,0.0104,0.9931,0.0108</t>
+  </si>
+  <si>
+    <t>0.9945,0.0014,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9926,0.0037,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9849,0.0073,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.8833,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0095,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0072,0.0043,0.9867,0.0042</t>
+  </si>
+  <si>
+    <t>0.0004,0.8391,0.9909,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0282,0.9750,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9980,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9216,0.0129,0.0821,0.0066</t>
+  </si>
+  <si>
+    <t>0.0186,0.0443,0.9530,0.0412</t>
+  </si>
+  <si>
+    <t>0.0052,0.0017,0.9939,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9893,0.9830,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.7777,0.9384,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.4031,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9743,0.9592,0.0003</t>
+  </si>
+  <si>
+    <t>0.0157,0.0008,0.0077,0.9863</t>
+  </si>
+  <si>
+    <t>0.0008,0.0004,0.0004,0.9993</t>
+  </si>
+  <si>
+    <t>0.0012,0.0013,0.0004,0.9991</t>
+  </si>
+  <si>
+    <t>0.0032,0.0007,0.0004,0.9985</t>
+  </si>
+  <si>
+    <t>0.0126,0.0011,0.0005,0.9951</t>
+  </si>
+  <si>
+    <t>0.0012,0.0005,0.0012,0.9986</t>
+  </si>
+  <si>
+    <t>0.0003,0.9814,0.9289,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.4671,0.9826,0.0008</t>
+  </si>
+  <si>
+    <t>0.0076,0.8104,0.8890,0.0065</t>
+  </si>
+  <si>
+    <t>0.0011,0.6913,0.9824,0.0015</t>
+  </si>
+  <si>
+    <t>0.0004,0.6691,0.9918,0.0002</t>
+  </si>
+  <si>
+    <t>0.0053,0.9681,0.1142,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0008,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9801,0.0208,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9940,0.0040,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9851,0.0045,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.9894,0.0054,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9891,0.0031,0.0006,0.0028</t>
+  </si>
+  <si>
+    <t>0.9834,0.0050,0.0012,0.0042</t>
+  </si>
+  <si>
+    <t>0.9751,0.0074,0.0154,0.0004</t>
+  </si>
+  <si>
+    <t>0.9967,0.0006,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9839,0.0038,0.0044,0.0039</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9838,0.0055,0.0073,0.0021</t>
+  </si>
+  <si>
+    <t>0.9959,0.0004,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9901,0.0029,0.0011,0.0021</t>
+  </si>
+  <si>
+    <t>0.0026,0.0017,0.9919,0.0068</t>
+  </si>
+  <si>
+    <t>0.1081,0.0427,0.8964,0.0030</t>
+  </si>
+  <si>
+    <t>0.9906,0.0003,0.0141,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0007,0.9939,0.0006</t>
+  </si>
+  <si>
+    <t>0.0094,0.9850,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.0025,0.9953,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0110,0.9853,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.0140,0.9787,0.0038,0.0048</t>
+  </si>
+  <si>
+    <t>0.0098,0.9896,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.9980,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.5772,0.5416,0.0078,0.0038</t>
+  </si>
+  <si>
+    <t>0.4733,0.3541,0.1158,0.0872</t>
+  </si>
+  <si>
+    <t>0.1131,0.0027,0.8642,0.0246</t>
+  </si>
+  <si>
+    <t>0.6003,0.0142,0.5074,0.0070</t>
+  </si>
+  <si>
+    <t>0.9255,0.0115,0.0584,0.0024</t>
+  </si>
+  <si>
+    <t>0.1199,0.2136,0.0798,0.5963</t>
+  </si>
+  <si>
+    <t>0.0033,0.9885,0.0040,0.0049</t>
+  </si>
+  <si>
+    <t>0.0026,0.9904,0.0205,0.0189</t>
+  </si>
+  <si>
+    <t>0.0004,0.9966,0.0016,0.0038</t>
+  </si>
+  <si>
+    <t>0.0007,0.9681,0.9395,0.0006</t>
+  </si>
+  <si>
+    <t>0.0277,0.9769,0.0064,0.0005</t>
+  </si>
+  <si>
+    <t>0.8254,0.2525,0.0031,0.0021</t>
+  </si>
+  <si>
+    <t>0.9355,0.0781,0.0027,0.0016</t>
+  </si>
+  <si>
+    <t>0.9915,0.0016,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.9844,0.0051,0.0037,0.0031</t>
+  </si>
+  <si>
+    <t>0.9904,0.0008,0.0007,0.0051</t>
+  </si>
+  <si>
+    <t>0.9641,0.0064,0.0157,0.0111</t>
+  </si>
+  <si>
+    <t>0.9890,0.0005,0.0006,0.0080</t>
+  </si>
+  <si>
+    <t>0.9911,0.0012,0.0035,0.0015</t>
+  </si>
+  <si>
+    <t>0.9760,0.0071,0.0133,0.0025</t>
+  </si>
+  <si>
+    <t>0.9935,0.0011,0.0018,0.0011</t>
+  </si>
+  <si>
+    <t>0.0021,0.8236,0.9703,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.3981,0.9946,0.0003</t>
+  </si>
+  <si>
+    <t>0.0060,0.0564,0.9830,0.0004</t>
+  </si>
+  <si>
+    <t>0.0340,0.0631,0.9275,0.0045</t>
+  </si>
+  <si>
+    <t>0.9764,0.0055,0.0058,0.0023</t>
+  </si>
+  <si>
+    <t>0.9192,0.0096,0.0502,0.0093</t>
+  </si>
+  <si>
+    <t>0.2917,0.0027,0.8683,0.0011</t>
+  </si>
+  <si>
+    <t>0.9456,0.0033,0.0538,0.0029</t>
+  </si>
+  <si>
+    <t>0.1048,0.0018,0.0060,0.9523</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0034,0.9991</t>
+  </si>
+  <si>
+    <t>0.0031,0.0020,0.0034,0.9959</t>
+  </si>
+  <si>
+    <t>0.0032,0.0001,0.0028,0.9961</t>
+  </si>
+  <si>
+    <t>0.0013,0.6552,0.9319,0.0047</t>
+  </si>
+  <si>
+    <t>0.9958,0.0013,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.1034,0.9057,0.0014,0.0043</t>
+  </si>
+  <si>
+    <t>0.9762,0.0088,0.0096,0.0017</t>
+  </si>
+  <si>
+    <t>0.3120,0.7725,0.0103,0.0017</t>
+  </si>
+  <si>
+    <t>0.9779,0.0010,0.0020,0.0191</t>
+  </si>
+  <si>
+    <t>0.7660,0.0049,0.0089,0.3188</t>
+  </si>
+  <si>
+    <t>0.9881,0.0024,0.0034,0.0027</t>
+  </si>
+  <si>
+    <t>0.0005,0.1592,0.9901,0.0118</t>
+  </si>
+  <si>
+    <t>0.9463,0.0002,0.0010,0.0805</t>
+  </si>
+  <si>
+    <t>0.9115,0.0031,0.0018,0.1041</t>
+  </si>
+  <si>
+    <t>0.0837,0.8776,0.0052,0.0172</t>
+  </si>
+  <si>
+    <t>0.9923,0.0017,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.8348,0.1236,0.0482,0.0077</t>
+  </si>
+  <si>
+    <t>0.0853,0.8508,0.0293,0.0237</t>
+  </si>
+  <si>
+    <t>0.6093,0.0421,0.3376,0.0025</t>
+  </si>
+  <si>
+    <t>0.8791,0.1368,0.0082,0.0020</t>
+  </si>
+  <si>
+    <t>0.9865,0.0011,0.0031,0.0061</t>
+  </si>
+  <si>
+    <t>0.9779,0.0018,0.0042,0.0126</t>
+  </si>
+  <si>
+    <t>0.9794,0.0061,0.0056,0.0038</t>
+  </si>
+  <si>
+    <t>0.9903,0.0002,0.0006,0.0103</t>
+  </si>
+  <si>
+    <t>0.9900,0.0020,0.0022,0.0022</t>
+  </si>
+  <si>
+    <t>0.9771,0.0093,0.0097,0.0014</t>
+  </si>
+  <si>
+    <t>0.9936,0.0014,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.9916,0.0020,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.7785,0.2574,0.0141,0.0060</t>
+  </si>
+  <si>
+    <t>0.6392,0.4998,0.0033,0.0013</t>
+  </si>
+  <si>
+    <t>0.6998,0.5173,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9425,0.0397,0.0113,0.0057</t>
+  </si>
+  <si>
+    <t>0.9916,0.0053,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9641,0.0103,0.0202,0.0039</t>
+  </si>
+  <si>
+    <t>0.9910,0.0023,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9149,0.1288,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.1043,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.8996,0.0948,0.0196,0.0051</t>
+  </si>
+  <si>
+    <t>0.0046,0.0050,0.9936,0.0009</t>
+  </si>
+  <si>
+    <t>0.0081,0.0041,0.9875,0.0062</t>
+  </si>
+  <si>
+    <t>0.0032,0.0009,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0114,0.0051,0.9879,0.0012</t>
+  </si>
+  <si>
+    <t>0.0080,0.0023,0.9923,0.0007</t>
+  </si>
+  <si>
+    <t>0.0083,0.0026,0.9926,0.0009</t>
+  </si>
+  <si>
+    <t>0.0045,0.0026,0.9892,0.0039</t>
+  </si>
+  <si>
+    <t>0.1024,0.0135,0.8628,0.0253</t>
+  </si>
+  <si>
+    <t>0.0501,0.0159,0.9375,0.0084</t>
+  </si>
+  <si>
+    <t>0.0681,0.1048,0.8615,0.0105</t>
+  </si>
+  <si>
+    <t>0.1277,0.0282,0.8621,0.0060</t>
+  </si>
+  <si>
+    <t>0.4318,0.3310,0.1450,0.0035</t>
+  </si>
+  <si>
+    <t>0.8393,0.0140,0.1978,0.0035</t>
+  </si>
+  <si>
+    <t>0.7531,0.0484,0.1299,0.0597</t>
+  </si>
+  <si>
+    <t>0.0607,0.0204,0.8997,0.0061</t>
+  </si>
+  <si>
+    <t>0.0277,0.9725,0.0029,0.0013</t>
+  </si>
+  <si>
+    <t>0.2353,0.8604,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9487,0.0905,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9589,0.0734,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.6975,0.5432,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.2780,0.4527,0.0746,0.1297</t>
+  </si>
+  <si>
+    <t>0.9545,0.0009,0.0629,0.0012</t>
+  </si>
+  <si>
+    <t>0.4475,0.0149,0.0399,0.5017</t>
+  </si>
+  <si>
+    <t>0.7794,0.0143,0.2571,0.0049</t>
+  </si>
+  <si>
+    <t>0.8112,0.0033,0.0948,0.0318</t>
+  </si>
+  <si>
+    <t>0.0048,0.0104,0.9781,0.0210</t>
+  </si>
+  <si>
+    <t>0.0142,0.0844,0.9257,0.0151</t>
+  </si>
+  <si>
+    <t>0.0281,0.0116,0.9680,0.0067</t>
+  </si>
+  <si>
+    <t>0.1527,0.0129,0.8591,0.0091</t>
+  </si>
+  <si>
+    <t>0.0008,0.0219,0.9948,0.0005</t>
+  </si>
+  <si>
+    <t>0.9879,0.0028,0.0003,0.0038</t>
+  </si>
+  <si>
+    <t>0.9807,0.0101,0.0050,0.0025</t>
+  </si>
+  <si>
+    <t>0.9741,0.0126,0.0110,0.0019</t>
+  </si>
+  <si>
+    <t>0.9888,0.0056,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9776,0.0225,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9862,0.0073,0.0011,0.0024</t>
+  </si>
+  <si>
+    <t>0.9852,0.0063,0.0015,0.0022</t>
+  </si>
+  <si>
+    <t>0.9965,0.0002,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.0179,0.1289,0.9647,0.0027</t>
+  </si>
+  <si>
+    <t>0.2628,0.6173,0.2900,0.0162</t>
+  </si>
+  <si>
+    <t>0.4543,0.0135,0.5336,0.0427</t>
+  </si>
+  <si>
+    <t>0.0064,0.0199,0.9916,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.0126,0.9914,0.0124</t>
+  </si>
+  <si>
+    <t>0.0066,0.0102,0.9823,0.0046</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.9975,0.0006</t>
+  </si>
+  <si>
+    <t>0.0920,0.0149,0.9123,0.0079</t>
+  </si>
+  <si>
+    <t>0.0009,0.0021,0.9978,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.0063,0.9921,0.0064</t>
+  </si>
+  <si>
+    <t>0.0395,0.0188,0.9157,0.0103</t>
+  </si>
+  <si>
+    <t>0.9148,0.0039,0.1153,0.0029</t>
+  </si>
+  <si>
+    <t>0.5996,0.0008,0.5307,0.0035</t>
+  </si>
+  <si>
+    <t>0.8166,0.0027,0.2343,0.0103</t>
+  </si>
+  <si>
+    <t>0.9868,0.0051,0.0017,0.0018</t>
+  </si>
+  <si>
+    <t>0.9890,0.0029,0.0015,0.0029</t>
+  </si>
+  <si>
+    <t>0.9815,0.0158,0.0029,0.0013</t>
+  </si>
+  <si>
+    <t>0.9915,0.0038,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9939,0.0006,0.0004,0.0028</t>
+  </si>
+  <si>
+    <t>0.9843,0.0104,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.9820,0.0165,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9911,0.0022,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.0130,0.0461,0.9360,0.0028</t>
+  </si>
+  <si>
+    <t>0.0020,0.0234,0.9906,0.0007</t>
+  </si>
+  <si>
+    <t>0.0048,0.0324,0.9897,0.0026</t>
+  </si>
+  <si>
+    <t>0.0180,0.0118,0.9550,0.0046</t>
+  </si>
+  <si>
+    <t>0.0015,0.0006,0.9925,0.0079</t>
+  </si>
+  <si>
+    <t>0.0194,0.0324,0.9409,0.0425</t>
+  </si>
+  <si>
+    <t>0.0087,0.0116,0.9826,0.0030</t>
+  </si>
+  <si>
+    <t>0.0381,0.0031,0.9340,0.0103</t>
+  </si>
+  <si>
+    <t>0.9711,0.0001,0.0003,0.0417</t>
+  </si>
+  <si>
+    <t>0.0138,0.0027,0.0032,0.9908</t>
+  </si>
+  <si>
+    <t>0.0098,0.0002,0.0005,0.9967</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.0014,0.0004,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.8113,0.0056,0.0010,0.2110</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4795,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
         <v>467</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5047,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
         <v>485</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
